--- a/docs/Mapping_casi_uso/matrimoni/Matr_Riconc_001.xlsx
+++ b/docs/Mapping_casi_uso/matrimoni/Matr_Riconc_001.xlsx
@@ -1128,7 +1128,7 @@
         <v>47</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>28</v>
@@ -1174,7 +1174,7 @@
         <v>51</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>28</v>
